--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.7557,0.1754,0.0384,0.0485</t>
-  </si>
-  <si>
-    <t>0.0184,0.0053,0.0080,0.9873</t>
-  </si>
-  <si>
-    <t>0.3239,0.0759,0.0062,0.6594</t>
-  </si>
-  <si>
-    <t>0.2696,0.0085,0.0313,0.7643</t>
-  </si>
-  <si>
-    <t>0.9950,0.0039,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9922,0.0014,0.0001,0.0026</t>
-  </si>
-  <si>
-    <t>0.9713,0.0410,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9929,0.0027,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9909,0.0024,0.0003,0.0025</t>
-  </si>
-  <si>
-    <t>0.9645,0.0541,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.9973,0.0010,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9929,0.0036,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.1667,0.6882,0.0851,0.1262</t>
-  </si>
-  <si>
-    <t>0.2158,0.0924,0.7646,0.0091</t>
-  </si>
-  <si>
-    <t>0.1036,0.0212,0.9386,0.0002</t>
-  </si>
-  <si>
-    <t>0.0617,0.1130,0.8797,0.0037</t>
-  </si>
-  <si>
-    <t>0.5007,0.1136,0.4812,0.0145</t>
-  </si>
-  <si>
-    <t>0.0293,0.9702,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.0339,0.9710,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.1279,0.9002,0.0095,0.0029</t>
-  </si>
-  <si>
-    <t>0.1592,0.8425,0.0334,0.0023</t>
-  </si>
-  <si>
-    <t>0.0158,0.9815,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.3785,0.0306,0.3857,0.2278</t>
-  </si>
-  <si>
-    <t>0.3185,0.0153,0.7618,0.0064</t>
-  </si>
-  <si>
-    <t>0.0116,0.0084,0.9730,0.0092</t>
-  </si>
-  <si>
-    <t>0.0146,0.4728,0.8354,0.0061</t>
-  </si>
-  <si>
-    <t>0.0316,0.0073,0.9745,0.0010</t>
-  </si>
-  <si>
-    <t>0.0071,0.0093,0.9799,0.0069</t>
-  </si>
-  <si>
-    <t>0.0009,0.0043,0.9906,0.0072</t>
-  </si>
-  <si>
-    <t>0.3430,0.6348,0.0493,0.0037</t>
-  </si>
-  <si>
-    <t>0.5727,0.1844,0.3292,0.0079</t>
-  </si>
-  <si>
-    <t>0.0003,0.0030,0.9954,0.0081</t>
-  </si>
-  <si>
-    <t>0.0127,0.9488,0.0528,0.0047</t>
-  </si>
-  <si>
-    <t>0.7322,0.2524,0.0754,0.0173</t>
-  </si>
-  <si>
-    <t>0.6010,0.2144,0.1830,0.0551</t>
-  </si>
-  <si>
-    <t>0.7319,0.4083,0.0077,0.0012</t>
-  </si>
-  <si>
-    <t>0.1127,0.8669,0.0760,0.0029</t>
-  </si>
-  <si>
-    <t>0.0162,0.7143,0.1421,0.2561</t>
-  </si>
-  <si>
-    <t>0.0458,0.0750,0.8979,0.0461</t>
-  </si>
-  <si>
-    <t>0.0403,0.2007,0.8694,0.0262</t>
-  </si>
-  <si>
-    <t>0.0202,0.0246,0.9067,0.0863</t>
-  </si>
-  <si>
-    <t>0.0063,0.3313,0.9490,0.0035</t>
-  </si>
-  <si>
-    <t>0.0012,0.9786,0.0106,0.0048</t>
-  </si>
-  <si>
-    <t>0.0063,0.0453,0.9643,0.0132</t>
-  </si>
-  <si>
-    <t>0.0402,0.5742,0.0090,0.7618</t>
-  </si>
-  <si>
-    <t>0.0062,0.9714,0.0081,0.0161</t>
-  </si>
-  <si>
-    <t>0.0253,0.9132,0.1226,0.0164</t>
-  </si>
-  <si>
-    <t>0.0180,0.9270,0.0779,0.0480</t>
-  </si>
-  <si>
-    <t>0.0047,0.1509,0.9170,0.0405</t>
-  </si>
-  <si>
-    <t>0.0001,0.0562,0.9952,0.0012</t>
-  </si>
-  <si>
-    <t>0.0061,0.0095,0.9496,0.0815</t>
-  </si>
-  <si>
-    <t>0.0029,0.0037,0.9945,0.0012</t>
-  </si>
-  <si>
-    <t>0.0038,0.0162,0.9732,0.0336</t>
-  </si>
-  <si>
-    <t>0.0029,0.0528,0.9779,0.0080</t>
-  </si>
-  <si>
-    <t>0.9168,0.1116,0.0078,0.0026</t>
-  </si>
-  <si>
-    <t>0.9694,0.0212,0.0065,0.0022</t>
-  </si>
-  <si>
-    <t>0.9694,0.0173,0.0059,0.0033</t>
-  </si>
-  <si>
-    <t>0.0213,0.0875,0.9495,0.0079</t>
-  </si>
-  <si>
-    <t>0.9809,0.0098,0.0023,0.0025</t>
-  </si>
-  <si>
-    <t>0.9848,0.0124,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9744,0.0278,0.0019,0.0015</t>
-  </si>
-  <si>
-    <t>0.0011,0.8538,0.8504,0.0029</t>
-  </si>
-  <si>
-    <t>0.0105,0.0883,0.9364,0.0329</t>
-  </si>
-  <si>
-    <t>0.0047,0.0034,0.9681,0.0704</t>
-  </si>
-  <si>
-    <t>0.0008,0.8725,0.9505,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9924,0.0186</t>
-  </si>
-  <si>
-    <t>0.0097,0.9216,0.3896,0.0007</t>
-  </si>
-  <si>
-    <t>0.0050,0.9879,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.1790,0.1017,0.8405,0.0028</t>
-  </si>
-  <si>
-    <t>0.5622,0.3064,0.3003,0.0414</t>
-  </si>
-  <si>
-    <t>0.0027,0.1072,0.9819,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.8935,0.9437,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.7929,0.9378,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9798,0.6754,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9822,0.3115,0.0008</t>
-  </si>
-  <si>
-    <t>0.0150,0.0232,0.1400,0.9313</t>
-  </si>
-  <si>
-    <t>0.0042,0.0025,0.0013,0.9972</t>
-  </si>
-  <si>
-    <t>0.0119,0.0035,0.0004,0.9955</t>
-  </si>
-  <si>
-    <t>0.0226,0.0020,0.0175,0.9770</t>
-  </si>
-  <si>
-    <t>0.0093,0.0051,0.0064,0.9918</t>
-  </si>
-  <si>
-    <t>0.0130,0.0046,0.0019,0.9929</t>
-  </si>
-  <si>
-    <t>0.0007,0.9788,0.2849,0.0028</t>
-  </si>
-  <si>
-    <t>0.0016,0.6595,0.9693,0.0003</t>
-  </si>
-  <si>
-    <t>0.0057,0.2872,0.9573,0.0026</t>
-  </si>
-  <si>
-    <t>0.0020,0.7238,0.9540,0.0010</t>
-  </si>
-  <si>
-    <t>0.0014,0.9473,0.7019,0.0024</t>
-  </si>
-  <si>
-    <t>0.0050,0.8148,0.8628,0.0020</t>
-  </si>
-  <si>
-    <t>0.9926,0.0045,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9788,0.0214,0.0011,0.0021</t>
-  </si>
-  <si>
-    <t>0.9672,0.0433,0.0015,0.0014</t>
-  </si>
-  <si>
-    <t>0.9895,0.0066,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9825,0.0065,0.0009,0.0045</t>
-  </si>
-  <si>
-    <t>0.9934,0.0037,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9836,0.0162,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.9891,0.0074,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9965,0.0005,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9922,0.0047,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0017,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9959,0.0020,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9930,0.0030,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9926,0.0051,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9939,0.0023,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9918,0.0065,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0032,0.0036,0.9829,0.0306</t>
-  </si>
-  <si>
-    <t>0.0365,0.0350,0.9308,0.0129</t>
-  </si>
-  <si>
-    <t>0.6128,0.0327,0.3667,0.0297</t>
-  </si>
-  <si>
-    <t>0.0221,0.0056,0.9823,0.0009</t>
-  </si>
-  <si>
-    <t>0.0365,0.9608,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.0409,0.9512,0.0045,0.0014</t>
-  </si>
-  <si>
-    <t>0.1235,0.8930,0.0046,0.0030</t>
-  </si>
-  <si>
-    <t>0.1328,0.9036,0.0041,0.0013</t>
-  </si>
-  <si>
-    <t>0.0283,0.9652,0.0104,0.0006</t>
-  </si>
-  <si>
-    <t>0.0032,0.9912,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.8047,0.3065,0.0085,0.0014</t>
-  </si>
-  <si>
-    <t>0.5207,0.0858,0.4953,0.0055</t>
-  </si>
-  <si>
-    <t>0.0742,0.0184,0.9066,0.0482</t>
-  </si>
-  <si>
-    <t>0.2850,0.3462,0.2959,0.0041</t>
-  </si>
-  <si>
-    <t>0.3256,0.1135,0.6481,0.0295</t>
-  </si>
-  <si>
-    <t>0.2675,0.1231,0.0860,0.7221</t>
-  </si>
-  <si>
-    <t>0.0150,0.9656,0.0120,0.0085</t>
-  </si>
-  <si>
-    <t>0.0063,0.9477,0.0134,0.0570</t>
-  </si>
-  <si>
-    <t>0.1305,0.5235,0.2273,0.3373</t>
-  </si>
-  <si>
-    <t>0.0004,0.8332,0.9667,0.0003</t>
-  </si>
-  <si>
-    <t>0.0209,0.9631,0.0844,0.0004</t>
-  </si>
-  <si>
-    <t>0.4941,0.5424,0.0388,0.0009</t>
-  </si>
-  <si>
-    <t>0.4172,0.6596,0.0202,0.0011</t>
-  </si>
-  <si>
-    <t>0.9575,0.0350,0.0021,0.0047</t>
-  </si>
-  <si>
-    <t>0.9850,0.0092,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.9873,0.0077,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.9628,0.0131,0.0169,0.0040</t>
-  </si>
-  <si>
-    <t>0.9948,0.0006,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.8858,0.0870,0.0486,0.0030</t>
-  </si>
-  <si>
-    <t>0.9683,0.0165,0.0056,0.0045</t>
-  </si>
-  <si>
-    <t>0.9720,0.0171,0.0044,0.0037</t>
-  </si>
-  <si>
-    <t>0.0005,0.8917,0.9633,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.3453,0.9889,0.0001</t>
-  </si>
-  <si>
-    <t>0.0115,0.1777,0.9587,0.0035</t>
-  </si>
-  <si>
-    <t>0.0423,0.2146,0.8853,0.0063</t>
-  </si>
-  <si>
-    <t>0.5906,0.1426,0.2875,0.0826</t>
-  </si>
-  <si>
-    <t>0.4544,0.1273,0.1794,0.4106</t>
-  </si>
-  <si>
-    <t>0.4902,0.0545,0.5827,0.0130</t>
-  </si>
-  <si>
-    <t>0.3853,0.4973,0.1416,0.0718</t>
-  </si>
-  <si>
-    <t>0.5602,0.0008,0.0011,0.6416</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.0006,0.9995</t>
-  </si>
-  <si>
-    <t>0.0029,0.0072,0.0004,0.9979</t>
-  </si>
-  <si>
-    <t>0.0586,0.0059,0.0077,0.9719</t>
-  </si>
-  <si>
-    <t>0.0037,0.9155,0.3579,0.0156</t>
-  </si>
-  <si>
-    <t>0.9755,0.0126,0.0029,0.0027</t>
-  </si>
-  <si>
-    <t>0.1851,0.8278,0.0132,0.0057</t>
-  </si>
-  <si>
-    <t>0.9662,0.0287,0.0032,0.0027</t>
-  </si>
-  <si>
-    <t>0.6233,0.4748,0.0177,0.0013</t>
-  </si>
-  <si>
-    <t>0.9333,0.0292,0.0178,0.0131</t>
-  </si>
-  <si>
-    <t>0.6522,0.0244,0.0451,0.2739</t>
-  </si>
-  <si>
-    <t>0.9794,0.0047,0.0044,0.0035</t>
-  </si>
-  <si>
-    <t>0.0040,0.0146,0.9852,0.0104</t>
-  </si>
-  <si>
-    <t>0.8204,0.0031,0.0146,0.1579</t>
-  </si>
-  <si>
-    <t>0.9774,0.0017,0.0022,0.0102</t>
-  </si>
-  <si>
-    <t>0.0689,0.9030,0.0105,0.0170</t>
-  </si>
-  <si>
-    <t>0.4397,0.5856,0.0331,0.0233</t>
-  </si>
-  <si>
-    <t>0.7400,0.1658,0.1606,0.0083</t>
-  </si>
-  <si>
-    <t>0.1104,0.8324,0.0913,0.0379</t>
-  </si>
-  <si>
-    <t>0.6567,0.3451,0.0836,0.0082</t>
-  </si>
-  <si>
-    <t>0.5743,0.3750,0.1393,0.0098</t>
-  </si>
-  <si>
-    <t>0.9867,0.0033,0.0005,0.0041</t>
-  </si>
-  <si>
-    <t>0.9828,0.0091,0.0005,0.0035</t>
-  </si>
-  <si>
-    <t>0.9905,0.0042,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9841,0.0023,0.0006,0.0067</t>
-  </si>
-  <si>
-    <t>0.9828,0.0077,0.0030,0.0018</t>
-  </si>
-  <si>
-    <t>0.9279,0.0642,0.0158,0.0046</t>
-  </si>
-  <si>
-    <t>0.9859,0.0034,0.0004,0.0040</t>
-  </si>
-  <si>
-    <t>0.9844,0.0053,0.0017,0.0031</t>
-  </si>
-  <si>
-    <t>0.2732,0.7451,0.0337,0.0239</t>
-  </si>
-  <si>
-    <t>0.4628,0.6169,0.0194,0.0015</t>
-  </si>
-  <si>
-    <t>0.7914,0.2960,0.0066,0.0025</t>
-  </si>
-  <si>
-    <t>0.6452,0.2054,0.2430,0.0112</t>
-  </si>
-  <si>
-    <t>0.9569,0.0676,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.8630,0.0886,0.0342,0.0272</t>
-  </si>
-  <si>
-    <t>0.9650,0.0333,0.0037,0.0024</t>
-  </si>
-  <si>
-    <t>0.6984,0.3825,0.0203,0.0034</t>
-  </si>
-  <si>
-    <t>0.0450,0.0700,0.9490,0.0047</t>
-  </si>
-  <si>
-    <t>0.8986,0.1354,0.0114,0.0026</t>
-  </si>
-  <si>
-    <t>0.0023,0.0054,0.9957,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0579,0.9934,0.0013</t>
-  </si>
-  <si>
-    <t>0.0060,0.0170,0.9867,0.0025</t>
-  </si>
-  <si>
-    <t>0.0025,0.0341,0.9773,0.0090</t>
-  </si>
-  <si>
-    <t>0.0056,0.0202,0.9744,0.0139</t>
-  </si>
-  <si>
-    <t>0.0060,0.0095,0.9905,0.0007</t>
-  </si>
-  <si>
-    <t>0.0064,0.0112,0.9852,0.0018</t>
-  </si>
-  <si>
-    <t>0.1389,0.2532,0.7217,0.0128</t>
-  </si>
-  <si>
-    <t>0.0998,0.0414,0.9174,0.0025</t>
-  </si>
-  <si>
-    <t>0.5322,0.1186,0.4323,0.0319</t>
-  </si>
-  <si>
-    <t>0.4868,0.1697,0.4012,0.0055</t>
-  </si>
-  <si>
-    <t>0.0495,0.8654,0.1489,0.0100</t>
-  </si>
-  <si>
-    <t>0.0537,0.0771,0.9022,0.0184</t>
-  </si>
-  <si>
-    <t>0.4926,0.2954,0.2658,0.0300</t>
-  </si>
-  <si>
-    <t>0.4017,0.4566,0.2344,0.1047</t>
-  </si>
-  <si>
-    <t>0.8625,0.2192,0.0090,0.0006</t>
-  </si>
-  <si>
-    <t>0.7817,0.2991,0.0135,0.0013</t>
-  </si>
-  <si>
-    <t>0.6763,0.4594,0.0081,0.0016</t>
-  </si>
-  <si>
-    <t>0.7503,0.3809,0.0062,0.0011</t>
-  </si>
-  <si>
-    <t>0.9305,0.1147,0.0032,0.0014</t>
-  </si>
-  <si>
-    <t>0.3030,0.3875,0.0434,0.2650</t>
-  </si>
-  <si>
-    <t>0.5697,0.0175,0.5952,0.0047</t>
-  </si>
-  <si>
-    <t>0.1492,0.0731,0.1572,0.7769</t>
-  </si>
-  <si>
-    <t>0.5243,0.0774,0.4734,0.0224</t>
-  </si>
-  <si>
-    <t>0.5819,0.0637,0.3413,0.0839</t>
-  </si>
-  <si>
-    <t>0.0011,0.0021,0.9887,0.0283</t>
-  </si>
-  <si>
-    <t>0.0528,0.4984,0.7446,0.0127</t>
-  </si>
-  <si>
-    <t>0.0276,0.5046,0.8322,0.0324</t>
-  </si>
-  <si>
-    <t>0.0705,0.2562,0.8069,0.0296</t>
-  </si>
-  <si>
-    <t>0.0070,0.8028,0.5928,0.0142</t>
-  </si>
-  <si>
-    <t>0.9868,0.0082,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.9934,0.0061,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9875,0.0050,0.0008,0.0030</t>
-  </si>
-  <si>
-    <t>0.9755,0.0247,0.0012,0.0024</t>
-  </si>
-  <si>
-    <t>0.9701,0.0411,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.9886,0.0040,0.0010,0.0019</t>
-  </si>
-  <si>
-    <t>0.9924,0.0016,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9770,0.0124,0.0050,0.0026</t>
-  </si>
-  <si>
-    <t>0.0727,0.3266,0.7314,0.0020</t>
-  </si>
-  <si>
-    <t>0.2297,0.2251,0.6912,0.0086</t>
-  </si>
-  <si>
-    <t>0.4399,0.0451,0.0311,0.5427</t>
-  </si>
-  <si>
-    <t>0.0159,0.0145,0.9801,0.0018</t>
-  </si>
-  <si>
-    <t>0.0070,0.1098,0.9413,0.0120</t>
-  </si>
-  <si>
-    <t>0.0388,0.0528,0.9381,0.0020</t>
-  </si>
-  <si>
-    <t>0.0002,0.0043,0.9981,0.0009</t>
-  </si>
-  <si>
-    <t>0.0176,0.0221,0.9616,0.0054</t>
-  </si>
-  <si>
-    <t>0.0022,0.0242,0.9898,0.0030</t>
-  </si>
-  <si>
-    <t>0.0080,0.0281,0.9732,0.0071</t>
-  </si>
-  <si>
-    <t>0.0645,0.2404,0.8026,0.0128</t>
-  </si>
-  <si>
-    <t>0.5121,0.0036,0.3357,0.0512</t>
-  </si>
-  <si>
-    <t>0.5937,0.0327,0.4763,0.0088</t>
-  </si>
-  <si>
-    <t>0.6538,0.0425,0.2821,0.0698</t>
-  </si>
-  <si>
-    <t>0.9514,0.0812,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.9876,0.0048,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9939,0.0046,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9745,0.0289,0.0037,0.0011</t>
-  </si>
-  <si>
-    <t>0.9811,0.0029,0.0006,0.0083</t>
-  </si>
-  <si>
-    <t>0.9842,0.0198,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0024,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9927,0.0039,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.0152,0.6071,0.6412,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0415,0.9834,0.0073</t>
-  </si>
-  <si>
-    <t>0.0028,0.2530,0.9648,0.0026</t>
-  </si>
-  <si>
-    <t>0.0325,0.0544,0.9482,0.0010</t>
-  </si>
-  <si>
-    <t>0.0050,0.0076,0.9861,0.0060</t>
-  </si>
-  <si>
-    <t>0.0263,0.0148,0.8617,0.2222</t>
-  </si>
-  <si>
-    <t>0.0322,0.0415,0.9438,0.0048</t>
-  </si>
-  <si>
-    <t>0.0495,0.1432,0.5172,0.4162</t>
-  </si>
-  <si>
-    <t>0.7638,0.0095,0.0167,0.2323</t>
-  </si>
-  <si>
-    <t>0.0773,0.0333,0.0062,0.9511</t>
-  </si>
-  <si>
-    <t>0.0220,0.0057,0.0022,0.9887</t>
-  </si>
-  <si>
-    <t>0.0053,0.0019,0.0007,0.9975</t>
-  </si>
-  <si>
-    <t>0.0238,0.0047,0.0061,0.9866</t>
-  </si>
-  <si>
-    <t>0.7363,0.1138,0.1138,0.0456</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.6701,0.1231,0.1486,0.0980</t>
+  </si>
+  <si>
+    <t>0.0212,0.0005,0.0005,0.9943</t>
+  </si>
+  <si>
+    <t>0.5737,0.0286,0.0201,0.4047</t>
+  </si>
+  <si>
+    <t>0.0128,0.0067,0.0059,0.9906</t>
+  </si>
+  <si>
+    <t>0.9955,0.0028,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9918,0.0033,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9814,0.0181,0.0040,0.0006</t>
+  </si>
+  <si>
+    <t>0.9868,0.0107,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9932,0.0039,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9839,0.0175,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9957,0.0016,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9947,0.0018,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.7283,0.0783,0.1543,0.0444</t>
+  </si>
+  <si>
+    <t>0.4190,0.0541,0.6597,0.0048</t>
+  </si>
+  <si>
+    <t>0.0295,0.1109,0.9577,0.0003</t>
+  </si>
+  <si>
+    <t>0.0709,0.1122,0.9022,0.0018</t>
+  </si>
+  <si>
+    <t>0.3588,0.0363,0.7425,0.0053</t>
+  </si>
+  <si>
+    <t>0.0029,0.9938,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0128,0.9855,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.4216,0.6776,0.0141,0.0067</t>
+  </si>
+  <si>
+    <t>0.0262,0.9685,0.0026,0.0021</t>
+  </si>
+  <si>
+    <t>0.0054,0.9901,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.3321,0.0197,0.6682,0.0373</t>
+  </si>
+  <si>
+    <t>0.1026,0.0065,0.8863,0.0211</t>
+  </si>
+  <si>
+    <t>0.1353,0.0314,0.8735,0.0029</t>
+  </si>
+  <si>
+    <t>0.2319,0.0662,0.7098,0.0427</t>
+  </si>
+  <si>
+    <t>0.0254,0.0156,0.9611,0.0066</t>
+  </si>
+  <si>
+    <t>0.0266,0.0091,0.9597,0.0097</t>
+  </si>
+  <si>
+    <t>0.0022,0.0021,0.9953,0.0013</t>
+  </si>
+  <si>
+    <t>0.2023,0.8312,0.0119,0.0073</t>
+  </si>
+  <si>
+    <t>0.6261,0.1375,0.3354,0.0053</t>
+  </si>
+  <si>
+    <t>0.0004,0.0047,0.9956,0.0056</t>
+  </si>
+  <si>
+    <t>0.0553,0.9223,0.0222,0.0058</t>
+  </si>
+  <si>
+    <t>0.7972,0.0889,0.0269,0.0679</t>
+  </si>
+  <si>
+    <t>0.8285,0.1304,0.0599,0.0066</t>
+  </si>
+  <si>
+    <t>0.7798,0.2972,0.0179,0.0022</t>
+  </si>
+  <si>
+    <t>0.0272,0.9572,0.0441,0.0020</t>
+  </si>
+  <si>
+    <t>0.0023,0.5926,0.1806,0.3797</t>
+  </si>
+  <si>
+    <t>0.0124,0.0757,0.9532,0.0154</t>
+  </si>
+  <si>
+    <t>0.0801,0.5900,0.6657,0.0326</t>
+  </si>
+  <si>
+    <t>0.0456,0.0076,0.6759,0.3829</t>
+  </si>
+  <si>
+    <t>0.0207,0.1964,0.9272,0.0068</t>
+  </si>
+  <si>
+    <t>0.0009,0.9842,0.0406,0.0013</t>
+  </si>
+  <si>
+    <t>0.0026,0.0470,0.9415,0.0526</t>
+  </si>
+  <si>
+    <t>0.1797,0.4348,0.1073,0.4683</t>
+  </si>
+  <si>
+    <t>0.0050,0.9478,0.0031,0.1176</t>
+  </si>
+  <si>
+    <t>0.0066,0.9575,0.1413,0.0075</t>
+  </si>
+  <si>
+    <t>0.0054,0.9766,0.0155,0.0087</t>
+  </si>
+  <si>
+    <t>0.0012,0.3170,0.9094,0.0198</t>
+  </si>
+  <si>
+    <t>0.0014,0.0692,0.9744,0.0116</t>
+  </si>
+  <si>
+    <t>0.0577,0.0105,0.9152,0.0301</t>
+  </si>
+  <si>
+    <t>0.1464,0.0031,0.9137,0.0040</t>
+  </si>
+  <si>
+    <t>0.0003,0.0015,0.9977,0.0023</t>
+  </si>
+  <si>
+    <t>0.0016,0.0645,0.9659,0.0173</t>
+  </si>
+  <si>
+    <t>0.9104,0.1432,0.0089,0.0012</t>
+  </si>
+  <si>
+    <t>0.8976,0.0090,0.1424,0.0012</t>
+  </si>
+  <si>
+    <t>0.9699,0.0063,0.0118,0.0047</t>
+  </si>
+  <si>
+    <t>0.0023,0.0110,0.9904,0.0073</t>
+  </si>
+  <si>
+    <t>0.9868,0.0089,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9899,0.0037,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9911,0.0107,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.9046,0.7362,0.0019</t>
+  </si>
+  <si>
+    <t>0.0295,0.2496,0.8823,0.0148</t>
+  </si>
+  <si>
+    <t>0.0069,0.0120,0.9799,0.0111</t>
+  </si>
+  <si>
+    <t>0.0003,0.9693,0.5282,0.0029</t>
+  </si>
+  <si>
+    <t>0.0121,0.0375,0.9750,0.0026</t>
+  </si>
+  <si>
+    <t>0.0740,0.8216,0.1458,0.0012</t>
+  </si>
+  <si>
+    <t>0.0018,0.9940,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.6009,0.0965,0.4563,0.0198</t>
+  </si>
+  <si>
+    <t>0.5025,0.4881,0.0825,0.0160</t>
+  </si>
+  <si>
+    <t>0.0003,0.0233,0.9908,0.0050</t>
+  </si>
+  <si>
+    <t>0.0004,0.8281,0.9729,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.8178,0.9570,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9732,0.6215,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9339,0.8745,0.0005</t>
+  </si>
+  <si>
+    <t>0.2049,0.0033,0.1000,0.7062</t>
+  </si>
+  <si>
+    <t>0.0457,0.0074,0.0022,0.9801</t>
+  </si>
+  <si>
+    <t>0.0283,0.0237,0.0054,0.9812</t>
+  </si>
+  <si>
+    <t>0.1495,0.0300,0.0062,0.9132</t>
+  </si>
+  <si>
+    <t>0.0184,0.0039,0.0830,0.9642</t>
+  </si>
+  <si>
+    <t>0.0056,0.0078,0.0013,0.9960</t>
+  </si>
+  <si>
+    <t>0.0006,0.9291,0.9226,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.8102,0.9594,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.3197,0.9687,0.0016</t>
+  </si>
+  <si>
+    <t>0.0036,0.6934,0.8097,0.0080</t>
+  </si>
+  <si>
+    <t>0.0018,0.8846,0.8704,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.9442,0.4499,0.0057</t>
+  </si>
+  <si>
+    <t>0.9630,0.0475,0.0052,0.0012</t>
+  </si>
+  <si>
+    <t>0.9617,0.0449,0.0036,0.0018</t>
+  </si>
+  <si>
+    <t>0.9772,0.0232,0.0026,0.0012</t>
+  </si>
+  <si>
+    <t>0.9949,0.0023,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9848,0.0125,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9869,0.0116,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9542,0.0575,0.0028,0.0023</t>
+  </si>
+  <si>
+    <t>0.9889,0.0091,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9905,0.0032,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.9931,0.0038,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9908,0.0062,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9939,0.0038,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9842,0.0132,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9942,0.0022,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9894,0.0072,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9941,0.0025,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.0032,0.0083,0.9570,0.0838</t>
+  </si>
+  <si>
+    <t>0.1119,0.0403,0.8644,0.0177</t>
+  </si>
+  <si>
+    <t>0.6751,0.0330,0.2918,0.0393</t>
+  </si>
+  <si>
+    <t>0.0867,0.0049,0.9174,0.0121</t>
+  </si>
+  <si>
+    <t>0.1991,0.8289,0.0145,0.0031</t>
+  </si>
+  <si>
+    <t>0.0386,0.9433,0.0143,0.0008</t>
+  </si>
+  <si>
+    <t>0.0476,0.9412,0.0039,0.0027</t>
+  </si>
+  <si>
+    <t>0.1262,0.8855,0.0144,0.0035</t>
+  </si>
+  <si>
+    <t>0.0159,0.9776,0.0099,0.0007</t>
+  </si>
+  <si>
+    <t>0.0215,0.9713,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.7538,0.3376,0.0157,0.0015</t>
+  </si>
+  <si>
+    <t>0.1476,0.5743,0.3548,0.0054</t>
+  </si>
+  <si>
+    <t>0.0329,0.0176,0.9637,0.0038</t>
+  </si>
+  <si>
+    <t>0.2799,0.4080,0.4220,0.0605</t>
+  </si>
+  <si>
+    <t>0.3505,0.4917,0.1739,0.0346</t>
+  </si>
+  <si>
+    <t>0.1341,0.3654,0.0535,0.7195</t>
+  </si>
+  <si>
+    <t>0.0092,0.9595,0.0261,0.0191</t>
+  </si>
+  <si>
+    <t>0.0044,0.9691,0.0042,0.0238</t>
+  </si>
+  <si>
+    <t>0.1107,0.7343,0.0145,0.2081</t>
+  </si>
+  <si>
+    <t>0.0032,0.9300,0.5836,0.0042</t>
+  </si>
+  <si>
+    <t>0.0277,0.9722,0.0083,0.0005</t>
+  </si>
+  <si>
+    <t>0.4416,0.6012,0.0352,0.0036</t>
+  </si>
+  <si>
+    <t>0.6246,0.4556,0.0223,0.0007</t>
+  </si>
+  <si>
+    <t>0.9248,0.0650,0.0174,0.0044</t>
+  </si>
+  <si>
+    <t>0.9468,0.0474,0.0141,0.0020</t>
+  </si>
+  <si>
+    <t>0.9873,0.0042,0.0009,0.0031</t>
+  </si>
+  <si>
+    <t>0.9812,0.0046,0.0029,0.0045</t>
+  </si>
+  <si>
+    <t>0.9772,0.0061,0.0024,0.0062</t>
+  </si>
+  <si>
+    <t>0.9249,0.0506,0.0227,0.0085</t>
+  </si>
+  <si>
+    <t>0.9882,0.0032,0.0010,0.0031</t>
+  </si>
+  <si>
+    <t>0.9642,0.0156,0.0085,0.0042</t>
+  </si>
+  <si>
+    <t>0.0021,0.8766,0.8408,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.7202,0.9736,0.0002</t>
+  </si>
+  <si>
+    <t>0.0046,0.1096,0.9841,0.0006</t>
+  </si>
+  <si>
+    <t>0.0068,0.5952,0.8661,0.0022</t>
+  </si>
+  <si>
+    <t>0.5555,0.1790,0.1383,0.1854</t>
+  </si>
+  <si>
+    <t>0.5125,0.1084,0.4358,0.0048</t>
+  </si>
+  <si>
+    <t>0.1370,0.0034,0.9460,0.0007</t>
+  </si>
+  <si>
+    <t>0.2208,0.4900,0.3846,0.0083</t>
+  </si>
+  <si>
+    <t>0.0334,0.0013,0.0024,0.9877</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.0007,0.9994</t>
+  </si>
+  <si>
+    <t>0.0088,0.0062,0.0022,0.9944</t>
+  </si>
+  <si>
+    <t>0.0462,0.0028,0.0039,0.9799</t>
+  </si>
+  <si>
+    <t>0.0019,0.8400,0.9050,0.0006</t>
+  </si>
+  <si>
+    <t>0.9899,0.0042,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.3771,0.6267,0.0445,0.0055</t>
+  </si>
+  <si>
+    <t>0.9832,0.0101,0.0014,0.0020</t>
+  </si>
+  <si>
+    <t>0.6716,0.4413,0.0102,0.0031</t>
+  </si>
+  <si>
+    <t>0.9333,0.0371,0.0086,0.0104</t>
+  </si>
+  <si>
+    <t>0.2605,0.0552,0.0223,0.7684</t>
+  </si>
+  <si>
+    <t>0.9727,0.0144,0.0053,0.0026</t>
+  </si>
+  <si>
+    <t>0.0060,0.0306,0.9655,0.0305</t>
+  </si>
+  <si>
+    <t>0.9348,0.0044,0.0245,0.0203</t>
+  </si>
+  <si>
+    <t>0.8954,0.0087,0.0227,0.0588</t>
+  </si>
+  <si>
+    <t>0.3089,0.7041,0.0269,0.0155</t>
+  </si>
+  <si>
+    <t>0.7304,0.2233,0.0172,0.0281</t>
+  </si>
+  <si>
+    <t>0.8771,0.0709,0.0565,0.0075</t>
+  </si>
+  <si>
+    <t>0.3358,0.6542,0.0425,0.0251</t>
+  </si>
+  <si>
+    <t>0.6780,0.2434,0.1325,0.0142</t>
+  </si>
+  <si>
+    <t>0.6234,0.3940,0.0401,0.0120</t>
+  </si>
+  <si>
+    <t>0.9798,0.0102,0.0028,0.0029</t>
+  </si>
+  <si>
+    <t>0.9773,0.0136,0.0016,0.0037</t>
+  </si>
+  <si>
+    <t>0.9822,0.0126,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.9863,0.0028,0.0006,0.0041</t>
+  </si>
+  <si>
+    <t>0.9871,0.0029,0.0010,0.0032</t>
+  </si>
+  <si>
+    <t>0.9919,0.0026,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9464,0.0500,0.0146,0.0030</t>
+  </si>
+  <si>
+    <t>0.9876,0.0041,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.3679,0.6853,0.0048,0.0091</t>
+  </si>
+  <si>
+    <t>0.4427,0.6774,0.0088,0.0009</t>
+  </si>
+  <si>
+    <t>0.4494,0.6351,0.0212,0.0019</t>
+  </si>
+  <si>
+    <t>0.9066,0.0825,0.0239,0.0142</t>
+  </si>
+  <si>
+    <t>0.9281,0.1225,0.0054,0.0011</t>
+  </si>
+  <si>
+    <t>0.8672,0.1387,0.0273,0.0087</t>
+  </si>
+  <si>
+    <t>0.9436,0.0806,0.0042,0.0013</t>
+  </si>
+  <si>
+    <t>0.9409,0.0540,0.0052,0.0060</t>
+  </si>
+  <si>
+    <t>0.0006,0.0077,0.9946,0.0048</t>
+  </si>
+  <si>
+    <t>0.9118,0.0647,0.0344,0.0060</t>
+  </si>
+  <si>
+    <t>0.0007,0.0064,0.9932,0.0037</t>
+  </si>
+  <si>
+    <t>0.0010,0.0119,0.9961,0.0005</t>
+  </si>
+  <si>
+    <t>0.0312,0.0226,0.9668,0.0012</t>
+  </si>
+  <si>
+    <t>0.0132,0.1462,0.9132,0.0124</t>
+  </si>
+  <si>
+    <t>0.0016,0.0041,0.9966,0.0006</t>
+  </si>
+  <si>
+    <t>0.0307,0.0024,0.9759,0.0033</t>
+  </si>
+  <si>
+    <t>0.0019,0.0121,0.9950,0.0003</t>
+  </si>
+  <si>
+    <t>0.0946,0.0870,0.9021,0.0022</t>
+  </si>
+  <si>
+    <t>0.4582,0.0608,0.6171,0.0051</t>
+  </si>
+  <si>
+    <t>0.4932,0.1194,0.5170,0.0190</t>
+  </si>
+  <si>
+    <t>0.1865,0.3059,0.5673,0.0032</t>
+  </si>
+  <si>
+    <t>0.2964,0.2007,0.5865,0.0148</t>
+  </si>
+  <si>
+    <t>0.4734,0.2121,0.3263,0.0184</t>
+  </si>
+  <si>
+    <t>0.1969,0.5266,0.2370,0.1476</t>
+  </si>
+  <si>
+    <t>0.4128,0.1637,0.4763,0.0109</t>
+  </si>
+  <si>
+    <t>0.6042,0.4554,0.0195,0.0005</t>
+  </si>
+  <si>
+    <t>0.9095,0.1433,0.0046,0.0019</t>
+  </si>
+  <si>
+    <t>0.3314,0.7492,0.0171,0.0015</t>
+  </si>
+  <si>
+    <t>0.9528,0.0605,0.0041,0.0021</t>
+  </si>
+  <si>
+    <t>0.9421,0.1215,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.2802,0.3642,0.5139,0.1158</t>
+  </si>
+  <si>
+    <t>0.5242,0.0604,0.5517,0.0083</t>
+  </si>
+  <si>
+    <t>0.6446,0.0662,0.2050,0.0964</t>
+  </si>
+  <si>
+    <t>0.3092,0.0144,0.7156,0.0378</t>
+  </si>
+  <si>
+    <t>0.6115,0.0371,0.4697,0.0156</t>
+  </si>
+  <si>
+    <t>0.0020,0.0076,0.9769,0.0441</t>
+  </si>
+  <si>
+    <t>0.0230,0.5812,0.7442,0.0374</t>
+  </si>
+  <si>
+    <t>0.0096,0.1372,0.9650,0.0037</t>
+  </si>
+  <si>
+    <t>0.0130,0.5258,0.9095,0.0078</t>
+  </si>
+  <si>
+    <t>0.0034,0.6137,0.6432,0.0304</t>
+  </si>
+  <si>
+    <t>0.9900,0.0033,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9888,0.0104,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9834,0.0080,0.0003,0.0033</t>
+  </si>
+  <si>
+    <t>0.9911,0.0072,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9728,0.0419,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.9746,0.0291,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.9915,0.0020,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9791,0.0145,0.0038,0.0016</t>
+  </si>
+  <si>
+    <t>0.0580,0.0470,0.9363,0.0019</t>
+  </si>
+  <si>
+    <t>0.2499,0.3173,0.5393,0.0054</t>
+  </si>
+  <si>
+    <t>0.5637,0.0697,0.2388,0.1272</t>
+  </si>
+  <si>
+    <t>0.0020,0.0198,0.9904,0.0021</t>
+  </si>
+  <si>
+    <t>0.0006,0.0325,0.9930,0.0008</t>
+  </si>
+  <si>
+    <t>0.0348,0.1084,0.8811,0.0132</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9988,0.0011</t>
+  </si>
+  <si>
+    <t>0.0062,0.1824,0.9695,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0207,0.9924,0.0027</t>
+  </si>
+  <si>
+    <t>0.0240,0.1025,0.9196,0.0084</t>
+  </si>
+  <si>
+    <t>0.1091,0.1525,0.7793,0.0362</t>
+  </si>
+  <si>
+    <t>0.3837,0.0409,0.6599,0.0130</t>
+  </si>
+  <si>
+    <t>0.5596,0.0163,0.5319,0.0123</t>
+  </si>
+  <si>
+    <t>0.6003,0.0317,0.4426,0.0205</t>
+  </si>
+  <si>
+    <t>0.9929,0.0053,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9776,0.0245,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.9927,0.0073,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9658,0.0465,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.9897,0.0024,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.9765,0.0312,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9883,0.0118,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9713,0.0267,0.0026,0.0027</t>
+  </si>
+  <si>
+    <t>0.0168,0.1071,0.9306,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0291,0.9906,0.0031</t>
+  </si>
+  <si>
+    <t>0.0005,0.0970,0.9845,0.0031</t>
+  </si>
+  <si>
+    <t>0.0387,0.1606,0.8597,0.0017</t>
+  </si>
+  <si>
+    <t>0.0093,0.0126,0.9877,0.0007</t>
+  </si>
+  <si>
+    <t>0.0463,0.0260,0.8544,0.1261</t>
+  </si>
+  <si>
+    <t>0.2110,0.0325,0.7879,0.0150</t>
+  </si>
+  <si>
+    <t>0.0105,0.1312,0.4483,0.5577</t>
+  </si>
+  <si>
+    <t>0.5954,0.0099,0.0215,0.4291</t>
+  </si>
+  <si>
+    <t>0.0233,0.0903,0.0048,0.9787</t>
+  </si>
+  <si>
+    <t>0.0446,0.0091,0.0066,0.9764</t>
+  </si>
+  <si>
+    <t>0.0043,0.0004,0.0013,0.9976</t>
+  </si>
+  <si>
+    <t>0.0082,0.0052,0.0012,0.9955</t>
+  </si>
+  <si>
+    <t>0.3009,0.1925,0.0692,0.6269</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2505,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2578,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2995,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3093,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,10 +3877,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,10 +4171,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4731,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,10 +4871,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,10 +4885,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4902,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,10 +5053,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5333,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
